--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512451_1ºBA1ºBBFINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512451_1ºBA1ºBBFINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7128</v>
+        <v>8.416399999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7107</v>
+        <v>8.9392</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0021</v>
+        <v>-0.5228</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4468</v>
+        <v>3.6162</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2141</v>
+        <v>0.327</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2327</v>
+        <v>3.2892</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5339</v>
+        <v>5.8424</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0508</v>
+        <v>0.2414</v>
       </c>
       <c r="L2" t="n">
-        <v>5.483</v>
+        <v>5.601</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.0871</v>
+        <v>-2.2262</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1633</v>
+        <v>0.0856</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.2503</v>
+        <v>-2.3118</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R2" t="n">
-        <v>2.8008</v>
+        <v>2.7263</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6061</v>
+        <v>1.1313</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1179</v>
+        <v>0.9331</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4882</v>
+        <v>0.1982</v>
       </c>
       <c r="V2" t="n">
-        <v>2.0594</v>
+        <v>2.1111</v>
       </c>
       <c r="W2" t="n">
-        <v>3.2592</v>
+        <v>3.3321</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="3">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.876</v>
+        <v>3.4878</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4608</v>
+        <v>4.0776</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5847</v>
+        <v>-0.5898</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9849</v>
+        <v>2.1193</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8136</v>
+        <v>-0.7974</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7985</v>
+        <v>2.9167</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9363</v>
+        <v>4.2179</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7126</v>
+        <v>-0.6054</v>
       </c>
       <c r="L3" t="n">
-        <v>4.6489</v>
+        <v>4.8233</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9514</v>
+        <v>-2.0986</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.101</v>
+        <v>-0.192</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.8504</v>
+        <v>-1.9065</v>
       </c>
       <c r="P3" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3092</v>
+        <v>0.2</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2755</v>
+        <v>0.0545</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0337</v>
+        <v>0.1456</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8625</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7975</v>
+        <v>0.6304</v>
       </c>
       <c r="F4" t="n">
-        <v>0.065</v>
+        <v>0.122</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0487</v>
+        <v>0.0679</v>
       </c>
       <c r="H4" t="n">
-        <v>0.991</v>
+        <v>1.0048</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9423</v>
+        <v>-0.9369</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2417</v>
+        <v>0.2797</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9197</v>
+        <v>0.9442</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.678</v>
+        <v>-0.6645</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1931</v>
+        <v>-0.2118</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0713</v>
+        <v>0.0605</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2643</v>
+        <v>-0.2724</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6138</v>
+        <v>0.4898</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5558</v>
+        <v>0.3507</v>
       </c>
       <c r="U4" t="n">
-        <v>0.058</v>
+        <v>0.1391</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,31 +799,31 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -877,31 +877,31 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5999</v>
+        <v>0.6079</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3984</v>
+        <v>0.1329</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6326</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2342</v>
+        <v>0.1329</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1939</v>
+        <v>0.1329</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1436</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3375</v>
+        <v>0.1329</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7852</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4653</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9791</v>
+        <v>0.1329</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3217</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6574</v>
+        <v>0.1329</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6002</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6002</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.7115</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8473</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1358</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.7194</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1356</v>
+        <v>-0.466</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1.717</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1356</v>
+        <v>-2.183</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1356</v>
+        <v>-0.1495</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.2105</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1356</v>
+        <v>-0.36</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.8965</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.5723</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.3242</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1356</v>
+        <v>-1.046</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.3618</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1356</v>
+        <v>-0.6842</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.8793</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.8205</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.0588</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.78</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2766</v>
+        <v>-0.7564</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1149</v>
+        <v>0.3465</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1618</v>
+        <v>-1.1029</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7564</v>
+        <v>-1.8633</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0189</v>
+        <v>-0.0689</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.7754</v>
+        <v>-1.7945</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3237</v>
+        <v>0.3747</v>
       </c>
       <c r="K9" t="n">
-        <v>0.12</v>
+        <v>0.1232</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2038</v>
+        <v>0.2515</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0802</v>
+        <v>-2.238</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.101</v>
+        <v>-0.192</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.9791</v>
+        <v>-2.046</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7599</v>
+        <v>0.3795</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0177</v>
+        <v>0.3018</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7775</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.0803</v>
+        <v>-0.0516</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7794</v>
+        <v>0.8384</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="10">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1879</v>
+        <v>-1.3655</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7936</v>
+        <v>-0.9606</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3943</v>
+        <v>-0.4048</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5997</v>
+        <v>-1.6284</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1022</v>
+        <v>-1.1063</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4975</v>
+        <v>-0.5221</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.478</v>
+        <v>-0.4613</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.638</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>0.16</v>
+        <v>0.1621</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1217</v>
+        <v>-1.1671</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4642</v>
+        <v>-0.4829</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6574</v>
+        <v>-0.6842</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4715</v>
+        <v>0.3477</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6847</v>
+        <v>0.4744</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2132</v>
+        <v>-0.1267</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>R. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3185</v>
+        <v>-1.3889</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6707</v>
+        <v>-0.8156</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3522</v>
+        <v>-0.5732</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.3557</v>
+        <v>-1.3334</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1179</v>
+        <v>-0.2571</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2378</v>
+        <v>-1.0763</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9122</v>
+        <v>-0.644</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5962</v>
+        <v>0.0205</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.316</v>
+        <v>-0.6645</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4434</v>
+        <v>-0.6895</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5217000000000001</v>
+        <v>-0.2776</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9218</v>
+        <v>-0.4118</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.0009</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.6007</v>
+        <v>0.3895</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4973</v>
+        <v>-0.1654</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9826</v>
+        <v>-0.1717</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5147</v>
+        <v>0.0062</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.2795</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6802</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="12">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4896</v>
+        <v>-1.4663</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.575</v>
+        <v>-1.6371</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.1707</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.3163</v>
+        <v>-3.2746</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4268</v>
+        <v>0.4192</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.7431</v>
+        <v>-3.6938</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.0083</v>
+        <v>-2.8997</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3417</v>
+        <v>0.3823</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.35</v>
+        <v>-3.282</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.308</v>
+        <v>-0.3749</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0851</v>
+        <v>0.0369</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3931</v>
+        <v>-0.4118</v>
       </c>
       <c r="P12" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0265</v>
+        <v>0.0293</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4335</v>
+        <v>0.2363</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.407</v>
+        <v>-0.207</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. LARDIES GUILLEN</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.6394</v>
+        <v>-1.983</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0447</v>
+        <v>-3.8016</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5946</v>
+        <v>1.8186</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.3154</v>
+        <v>-3.3611</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2443</v>
+        <v>-1.1161</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.0711</v>
+        <v>-2.245</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.658</v>
+        <v>-1.8375</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02</v>
+        <v>-0.549</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.678</v>
+        <v>-1.2885</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6574</v>
+        <v>-1.5236</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2643</v>
+        <v>-0.5671</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3931</v>
+        <v>-0.9565</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.921</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4001</v>
+        <v>2.5316</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4643</v>
+        <v>0.826</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3867</v>
+        <v>0.6774</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0776</v>
+        <v>0.1486</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2598</v>
+        <v>0.9416</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2598</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.9121</v>
+        <v>-3.6061</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.9776</v>
+        <v>-1.69</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9346</v>
+        <v>-1.916</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.1107</v>
+        <v>-3.1542</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3806</v>
+        <v>0.334</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.4913</v>
+        <v>-3.4882</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2474</v>
+        <v>0.3588</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3596</v>
+        <v>1.3958</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.1122</v>
+        <v>-1.037</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.3581</v>
+        <v>-3.5131</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.979</v>
+        <v>-1.0618</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.3791</v>
+        <v>-2.4513</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5417</v>
+        <v>-0.1724</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2244</v>
+        <v>-0.1015</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3173</v>
+        <v>-0.0708</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-7.0206</v>
+        <v>-6.7359</v>
       </c>
       <c r="E15" t="n">
-        <v>-6.2109</v>
+        <v>-5.8373</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8098</v>
+        <v>-0.8987000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.0151</v>
+        <v>-6.0722</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.9647</v>
+        <v>-3.963</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.0504</v>
+        <v>-2.1092</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.7281</v>
+        <v>-3.6407</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.928</v>
+        <v>-3.8434</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2</v>
+        <v>0.2026</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.287</v>
+        <v>-2.4315</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0367</v>
+        <v>-0.1197</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.2503</v>
+        <v>-2.3118</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6257</v>
+        <v>-0.2674</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2822</v>
+        <v>-0.0544</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3435</v>
+        <v>-0.213</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.659599999999999</v>
+        <v>-3.7627</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4139999999999997</v>
+        <v>2.184300000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.0736</v>
+        <v>-5.946999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-13.8474</v>
+        <v>-13.6846</v>
       </c>
       <c r="H16" t="n">
-        <v>-5.0677</v>
+        <v>-5.0133</v>
       </c>
       <c r="I16" t="n">
-        <v>-8.779799999999998</v>
+        <v>-8.671399999999998</v>
       </c>
       <c r="J16" t="n">
-        <v>2.483399999999999</v>
+        <v>3.702599999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.5977</v>
+        <v>-1.9416</v>
       </c>
       <c r="L16" t="n">
-        <v>5.081299999999998</v>
+        <v>5.644</v>
       </c>
       <c r="M16" t="n">
-        <v>-16.3309</v>
+        <v>-17.3874</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.4699</v>
+        <v>-3.0719</v>
       </c>
       <c r="O16" t="n">
-        <v>-13.8607</v>
+        <v>-14.3154</v>
       </c>
       <c r="P16" t="n">
-        <v>5.001499999999998</v>
+        <v>4.868300000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>-11.0032</v>
+        <v>-10.7104</v>
       </c>
       <c r="R16" t="n">
-        <v>16.0046</v>
+        <v>15.5791</v>
       </c>
       <c r="S16" t="n">
-        <v>3.745700000000001</v>
+        <v>3.6777</v>
       </c>
       <c r="T16" t="n">
-        <v>3.4353</v>
+        <v>3.521100000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3102999999999997</v>
+        <v>0.1566999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4406</v>
+        <v>1.3757</v>
       </c>
       <c r="W16" t="n">
-        <v>5.4982</v>
+        <v>5.6711</v>
       </c>
       <c r="X16" t="n">
-        <v>-4.057600000000001</v>
+        <v>-4.295399999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.6971</v>
+        <v>4.3958</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1845</v>
+        <v>2.6037</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5126</v>
+        <v>1.7921</v>
       </c>
       <c r="G17" t="n">
-        <v>4.8875</v>
+        <v>4.8415</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3876</v>
+        <v>0.3222</v>
       </c>
       <c r="I17" t="n">
-        <v>4.4999</v>
+        <v>4.5193</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2833</v>
+        <v>3.3742</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.518</v>
+        <v>-0.5003</v>
       </c>
       <c r="L17" t="n">
-        <v>3.8014</v>
+        <v>3.8744</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6042</v>
+        <v>1.4673</v>
       </c>
       <c r="N17" t="n">
-        <v>0.9056</v>
+        <v>0.8225</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6986</v>
+        <v>0.6448</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.91</v>
+        <v>-0.1994</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2177</v>
+        <v>0.0074</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6923</v>
+        <v>-0.2068</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.0803</v>
+        <v>-0.0516</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1195</v>
+        <v>1.1695</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="18">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.2213</v>
+        <v>3.7452</v>
       </c>
       <c r="E18" t="n">
-        <v>3.7869</v>
+        <v>4.1725</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5656</v>
+        <v>-0.4273</v>
       </c>
       <c r="G18" t="n">
-        <v>2.756</v>
+        <v>2.7253</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0015</v>
+        <v>-1.0597</v>
       </c>
       <c r="I18" t="n">
-        <v>3.7576</v>
+        <v>3.785</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8432</v>
+        <v>3.941</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.5413</v>
       </c>
       <c r="L18" t="n">
-        <v>4.4013</v>
+        <v>4.4823</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0872</v>
+        <v>-1.2157</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4435</v>
+        <v>-0.5184</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6437</v>
+        <v>-0.6973</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3944</v>
+        <v>-0.8701</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5157</v>
+        <v>-0.2953</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8788</v>
+        <v>-0.5748</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.9279</v>
+        <v>2.7349</v>
       </c>
       <c r="E19" t="n">
-        <v>3.96</v>
+        <v>3.8914</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0321</v>
+        <v>-1.1565</v>
       </c>
       <c r="G19" t="n">
-        <v>4.4912</v>
+        <v>4.5035</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7872</v>
+        <v>1.759</v>
       </c>
       <c r="I19" t="n">
-        <v>2.704</v>
+        <v>2.7445</v>
       </c>
       <c r="J19" t="n">
-        <v>5.6428</v>
+        <v>5.781</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3596</v>
+        <v>1.3958</v>
       </c>
       <c r="L19" t="n">
-        <v>4.2832</v>
+        <v>4.3852</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1517</v>
+        <v>-1.2775</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4275</v>
+        <v>0.3632</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5792</v>
+        <v>-1.6407</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.4582</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7181</v>
+        <v>0.4209</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.021</v>
+        <v>0.0374</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8597</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="20">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1473</v>
+        <v>1.9663</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3647</v>
+        <v>0.9525</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7826</v>
+        <v>1.0138</v>
       </c>
       <c r="G20" t="n">
-        <v>3.6306</v>
+        <v>3.694</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8586</v>
+        <v>4.9879</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.228</v>
+        <v>-1.2939</v>
       </c>
       <c r="J20" t="n">
-        <v>4.3479</v>
+        <v>4.6096</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1461</v>
+        <v>4.3825</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2019</v>
+        <v>0.2271</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7173</v>
+        <v>-0.9156</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7126</v>
+        <v>0.6054</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4299</v>
+        <v>-1.521</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2172</v>
+        <v>-0.0725</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2822</v>
+        <v>-0.0544</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4994</v>
+        <v>-0.018</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.7005</v>
+        <v>-1.6553</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.7005</v>
+        <v>-1.6553</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5042</v>
+        <v>1.0596</v>
       </c>
       <c r="E21" t="n">
-        <v>2.754</v>
+        <v>2.5063</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2498</v>
+        <v>-1.4467</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3824</v>
+        <v>-0.3758</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.3783</v>
+        <v>-2.3533</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9959</v>
+        <v>1.9774</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6474</v>
+        <v>0.7557</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.9922</v>
+        <v>-1.9191</v>
       </c>
       <c r="L21" t="n">
-        <v>2.6396</v>
+        <v>2.6747</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0298</v>
+        <v>-1.1315</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3861</v>
+        <v>-0.4342</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6437</v>
+        <v>-0.6973</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2266</v>
+        <v>0.7665</v>
       </c>
       <c r="T21" t="n">
-        <v>0.647</v>
+        <v>0.2501</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5796</v>
+        <v>0.5164</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2244</v>
+        <v>0.2358</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2418</v>
+        <v>1.0055</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0174</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1855</v>
+        <v>1.1098</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0349</v>
+        <v>-0.0863</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2204</v>
+        <v>1.1961</v>
       </c>
       <c r="J22" t="n">
-        <v>2.0797</v>
+        <v>2.1084</v>
       </c>
       <c r="K22" t="n">
-        <v>0.08</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>1.9997</v>
+        <v>2.0263</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8942</v>
+        <v>-0.9986</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1149</v>
+        <v>-0.1684</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7793</v>
+        <v>-0.8302</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.361</v>
+        <v>-0.2898</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1623</v>
+        <v>-0.1292</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5233</v>
+        <v>-0.1606</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.3335</v>
+        <v>-0.751</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2711</v>
+        <v>-2.8783</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9375</v>
+        <v>2.1273</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4443</v>
+        <v>-0.4571</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4981</v>
+        <v>0.4798</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9423</v>
+        <v>-0.9369</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5704</v>
+        <v>-1.4652</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3363</v>
+        <v>-0.2822</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2341</v>
+        <v>-1.183</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1261</v>
+        <v>1.0081</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8343</v>
+        <v>0.7619</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2918</v>
+        <v>0.2461</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7489</v>
+        <v>-0.1839</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0401</v>
+        <v>0.2547</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.789</v>
+        <v>-0.4386</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4835</v>
+        <v>-0.8276</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9255</v>
+        <v>-1.527</v>
       </c>
       <c r="F24" t="n">
-        <v>0.442</v>
+        <v>0.6994</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3743</v>
+        <v>0.3083</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6385</v>
+        <v>1.5938</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2642</v>
+        <v>-1.2855</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4162</v>
+        <v>-0.3669</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7398</v>
+        <v>0.7595</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.156</v>
+        <v>-1.1264</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7905</v>
+        <v>0.6752</v>
       </c>
       <c r="N24" t="n">
-        <v>0.8987000000000001</v>
+        <v>0.8343</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1082</v>
+        <v>-0.1591</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6785</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.509</v>
+        <v>-0.1864</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1696</v>
+        <v>-0.6952</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.7794</v>
+        <v>-0.8384</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.7794</v>
+        <v>-0.8384</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.5996</v>
+        <v>-3.0449</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9632</v>
+        <v>-2.4897</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6364</v>
+        <v>-0.5552</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.9295</v>
+        <v>-0.8856000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3679</v>
+        <v>0.447</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.2973</v>
+        <v>-1.3326</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.0488</v>
+        <v>-0.8897</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1472</v>
+        <v>0.2772</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.196</v>
+        <v>-1.1669</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1194</v>
+        <v>0.0041</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2207</v>
+        <v>0.1698</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1013</v>
+        <v>-0.1657</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.6005</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7296</v>
+        <v>-0.2704</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7735</v>
+        <v>-0.5427</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0439</v>
+        <v>0.2722</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3401</v>
+        <v>-0.3311</v>
       </c>
       <c r="W25" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.646</v>
+        <v>-3.758</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.0584</v>
+        <v>-2.29</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.5876</v>
+        <v>-1.4679</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.7215</v>
+        <v>-1.7792</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.0553</v>
+        <v>-1.0771</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6662</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.478</v>
+        <v>-0.4608</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.598</v>
+        <v>-0.5824</v>
       </c>
       <c r="L26" t="n">
-        <v>0.12</v>
+        <v>0.1216</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.2435</v>
+        <v>-1.3184</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.4573</v>
+        <v>-0.4947</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.7862</v>
+        <v>-0.8236</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.6005</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R26" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.1414</v>
       </c>
       <c r="T26" t="n">
-        <v>0.4202</v>
+        <v>0.1181</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4844</v>
+        <v>-0.2596</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>3.6596</v>
+        <v>5.756100000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>4.073699999999998</v>
+        <v>5.946900000000002</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4141999999999999</v>
+        <v>-0.1907000000000003</v>
       </c>
       <c r="G27" t="n">
-        <v>13.8474</v>
+        <v>13.6847</v>
       </c>
       <c r="H27" t="n">
-        <v>5.0679</v>
+        <v>5.0133</v>
       </c>
       <c r="I27" t="n">
-        <v>8.779800000000002</v>
+        <v>8.671300000000002</v>
       </c>
       <c r="J27" t="n">
-        <v>16.3309</v>
+        <v>17.3873</v>
       </c>
       <c r="K27" t="n">
-        <v>2.470199999999998</v>
+        <v>3.0718</v>
       </c>
       <c r="L27" t="n">
-        <v>13.861</v>
+        <v>14.3153</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.4835</v>
+        <v>-3.7026</v>
       </c>
       <c r="N27" t="n">
-        <v>2.5976</v>
+        <v>1.9414</v>
       </c>
       <c r="O27" t="n">
-        <v>-5.0811</v>
+        <v>-5.644</v>
       </c>
       <c r="P27" t="n">
-        <v>-5.0016</v>
+        <v>-4.8684</v>
       </c>
       <c r="Q27" t="n">
-        <v>-16.0048</v>
+        <v>-15.5791</v>
       </c>
       <c r="R27" t="n">
-        <v>11.0032</v>
+        <v>10.7107</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.7457</v>
+        <v>-1.6844</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.3104</v>
+        <v>-0.1568000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.4355</v>
+        <v>-1.5276</v>
       </c>
       <c r="V27" t="n">
-        <v>-1.4407</v>
+        <v>-1.3759</v>
       </c>
       <c r="W27" t="n">
-        <v>4.0576</v>
+        <v>4.295199999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>-5.4983</v>
+        <v>-5.6712</v>
       </c>
     </row>
   </sheetData>
